--- a/手动验收清单-WM3-WM13-20260831.xlsx
+++ b/手动验收清单-WM3-WM13-20260831.xlsx
@@ -71,7 +71,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -93,11 +93,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -121,6 +165,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,11 +705,11 @@
           <t>A. 基础业务链（docs/04 WM3 验收表）</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="10" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -913,11 +959,11 @@
           <t>B. UX 修复专项（20260831 批次 W1-W12，演示数据已就绪）</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -1128,7 +1174,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>创建订单弹窗看收款方式下拉</t>
+          <t>确认收款弹窗看收款方式下拉</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1230,11 +1276,11 @@
           <t>第一链：超管感知 → 处理 → 闭环（核心，约 12 分钟）</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="10" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -1418,11 +1464,11 @@
           <t>第二链：S1 撤销反例（本模块灵魂设计，约 5 分钟）</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="n">
@@ -1474,11 +1520,11 @@
           <t>第三链：staff 权限视角（S2 验证，约 5 分钟）</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -1530,11 +1576,11 @@
           <t>第四链：细节快扫（约 3 分钟）</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="n">

--- a/手动验收清单-WM3-WM13-20260831.xlsx
+++ b/手动验收清单-WM3-WM13-20260831.xlsx
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>小程序（13800008888 演示家长，演示孩有 WM11-DEMO paid 订单）对订单申请退款</t>
+          <t>小程序 7777（WM3 异常态演示家长）对临期孩的正式年费订单申请退款（W4 动线修正：8888 名下历史遗留零订单，实测换 7777）</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
